--- a/meta/en/1-3-1-a.xlsx
+++ b/meta/en/1-3-1-a.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист 1" sheetId="2" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>1. Indicator information</t>
   </si>
@@ -109,62 +109,98 @@
     <t>+996 (0312) 32 46 52</t>
   </si>
   <si>
-    <t>Population covered by pensions or social allowances</t>
-  </si>
-  <si>
-    <t>Pension (allowance) recipient is an individual covered by a pension (allowance). 
-Pension is an insurance benefit payable in the insured event to the insured person in the amount and under the conditions provided for in the legislation on state pension social insurance.
-The number of pension recipients is the number of persons as of the end (beginning) of the reporting year covered by monthly payment on the terms and conditions stipulated by the legislation on pension provision. The total number of pension recipients is calculated based on the number of personal pensioners’ accounts registered with the Social Fund, other ministries and departments, as well as the Non-State Pension Fund.
-Mandatory social security is a system of social and economic measures enshrined in legislation to guarantee material security for citizens in old age, in the event of disability or loss of breadwinner in the family; and to provide benefits to families with relatively low average per capita incomes, if they are not entitled to a pension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Kyrgyz legislation provides for legal regulation of guaranteed minimum social standards to ensure the basic living needs of the population, including social standards for pensions.
-Insured citizens of the Kyrgyz Republic, foreign citizens and stateless persons residing in the country who contribute to the state pension social insurance on the basis of and under the conditions stipulated in the Law of the Kyrgyz Republic on the State Social Insurance:627} have the right to pensions under the state pension social insurance (hereinafter - pensions). </t>
-  </si>
-  <si>
-    <t>The Social Fund of the Kyrgyz Republic, the Ministry of Labour and Social Development of the Kyrgyz Republic, the Accumulative Pension Fund of the Kyrgyz Republic, ministries and departments with pension bodies submit administrative data according to the approved state statistical reporting forms.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On an annual basis, the NSC collects and processes Report on the social benefits’ recipients and monthly allowances’ amount, Report on the number of pensioners and their monthly pensions, Report on the number of pensioners registered with the Accumulative Pension Fund and their monthly pensions, Report on the number of pensioners in security, defence and law enforcement agencies and their pension amount according to the statistical reporting forms. </t>
-  </si>
-  <si>
-    <t>The ratio of the number of pensioners registered in all pension bodies and the number of citizens covered by social benefits to the total population.</t>
-  </si>
-  <si>
-    <t>Supervisory authorities monitor personal accounts and pensions and benefits amount.</t>
-  </si>
-  <si>
-    <t>Data are available since 2007.</t>
-  </si>
-  <si>
     <t>National level</t>
   </si>
   <si>
-    <t>Pension age is is established by the Kyrgyz Republic laws</t>
-  </si>
-  <si>
-    <t>Law of the Kyrgyz Republic on the State Pension Social Insurance:  http://cbd.minjust.gov.kg/act/view/ru-ru/557/310?cl=ru-ru</t>
-  </si>
-  <si>
     <t>www.stat.gov.kg</t>
   </si>
   <si>
     <t>The National Statistical Committee of the Kyrgyz Republic (Social Statistics Division)</t>
   </si>
   <si>
-    <t>1.3.1.a Proportion of the population receiving MSB/"Üy-bülögö kömök" (family assistance) to the total population</t>
+    <t>"State social benefits are financial support guaranteed by the Constitution of the Kyrgyz Republic to low-income families and citizens, as well as to disabled citizens in the absence of the right to social protection. The following types of state benefits are established: 1) monthly allowance for citizens (families) with 3 or more children aged 3 to 16 years "uy-bulogo komok"; 2) monthly allowance for persons who are not eligible for pension provision "social benefit".                                                                                                                                                                                  The recipient of benefits is an individual to whom benefits are paid.  Compulsory social security is a system of socio–economic measures stipulated in legislation that guarantee the material security of citizens in old age, in case of disability, in case of loss of a breadwinner in the family; providing benefits to families with relatively low per capita incomes, in the absence of their right to social protection.        
+The amount of monthly State social benefits awarded includes information about the social benefits awarded to their recipients, including recipients living in boarding schools for the disabled. These amounts are calculated according to the personal accounts of all recipients of social benefits.  
+The average amount of monthly State social benefits awarded is calculated as the ratio of the total amount of monthly benefits awarded to all recipients registered with the social protection authorities to their total number.  
+A low-income family is a family with an income per family member below the guaranteed minimum consumption level.  
+Family composition - the family includes people living together who are related, who run a common household and have a common budget. 
+The guaranteed minimum level of consumption is a social standard established annually by the Government of the Kyrgyz Republic, calculated based on the budget and the state of the economy, taking into account the minimum consumer budget, which allows low–income families and citizens to provide a vital level of consumption through subsidies. Permanent population - the population permanently residing in the territory at the time of the census, including those temporarily absent. In the inter-census period, a current estimate of the permanent population is made based on the census data and taking into account information from the current registration of demographic events.
+"</t>
+  </si>
+  <si>
+    <t>"State social benefits are financial support guaranteed by the Constitution of the Kyrgyz Republic to low-income families and citizens, as well as to disabled citizens in the absence of the right to pension provision. 
+The following types of state benefits have been established:
+• a single monthly allowance for low-income families and citizens; 
+• Monthly social security allowance. 
+Monthly social benefits are paid to the following persons:
+• disabled children with cerebral palsy and children with HIV or AIDS under the age of 18; 
+• persons with disabilities from childhood of groups I, II and III; 
+• disabled persons of groups I, II and III - in the absence of the right to pension provision; 
+• elderly citizens - in the absence of the right to pension provision; 
+• heroine mothers - in the absence of the right to pension provision; 
+• children in case of loss of the breadwinner – in the absence of the right to pension provision. 
+"</t>
+  </si>
+  <si>
+    <t>Social services are services of a medical and domestic nature provided by social assistance agencies in need of outside care and assistance at home or in inpatient facilities. State social benefits are financial support guaranteed by the Constitution of the Kyrgyz Republic to low-income families and citizens, as well as to disabled citizens in the absence of the right to pension provision.</t>
+  </si>
+  <si>
+    <t>To carry out statistical monitoring, the official statistical reporting form No. 2-sobes (state pension) "Summary report on the payment and required amount of a single monthly and social benefits" is used.</t>
+  </si>
+  <si>
+    <t>"The administrative data of the Ministry of Labor, Social Security and Migration of the Kyrgyz Republic (MTSOM) is subject to coverage.
+The method of observation is continuous observation: official statistical reporting.
+The object of statistical observation is the number of recipients of various types of state benefits, as well as total benefit payments (by category) and average amounts of benefits.
+The units of observation are statistical units that organize compulsory social security.                                                                                                                                                                                                                                                                                                                The main indicators of statistical observation 
+Social protection statistics have their own specific indicators for a comprehensive description of the research object.  
+• The number and composition of those receiving various types of State benefits, as well as total benefit payments (by category); 
+• Average amounts of benefits, including by recipient group; 
+• the network of boarding schools for the disabled, the number of places in them and the number of people living in them; 
+• the amount of social benefits to the population and their ratio to the cost of living;
+"</t>
+  </si>
+  <si>
+    <t>The proportion of the population receiving "uy-bulogo komok" benefits to the total population is equal to: The number of people receiving "uy-bulogo komok" benefits is divided by the total population and multiplied by 100%.</t>
+  </si>
+  <si>
+    <t>The data has been available since 2007</t>
+  </si>
+  <si>
+    <t>"• The Law of the Kyrgyz Republic "On Official Statistics" dated July 8, 2019 No. 82; 
+• The Law of the Kyrgyz Republic dated July 28, 2017 No. 163 "On State Benefits in the Kyrgyz Republic"; 
+• The Law of the Kyrgyz Republic dated March 3, 2023 No. 49 "On the Rights and Guarantees of persons with disabilities in the Kyrgyz Republic"; 
+• Resolution of the Government of the Kyrgyz Republic dated September 18, 2018 No. 434 "On the appointment and payment of temporary disability benefits, maternity benefits, funeral benefits"; 
+"</t>
+  </si>
+  <si>
+    <t>1.3.1.a Proportion of the population receiving  "Üy-bülögö kömök" (family assistance) to the total population</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -239,30 +275,38 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -608,8 +652,8 @@
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>44</v>
+      <c r="B4" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -623,7 +667,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -655,7 +699,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -664,28 +708,28 @@
       </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:2" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>31</v>
+      <c r="B12" s="9" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>33</v>
+      <c r="B14" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -698,16 +742,16 @@
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="231.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>35</v>
+      <c r="B17" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -716,12 +760,12 @@
       </c>
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>36</v>
+      <c r="B19" s="9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -734,9 +778,7 @@
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="B21" s="6"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -749,7 +791,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -757,22 +799,20 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="243.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="6"/>
+    </row>
+    <row r="26" spans="1:2" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="9" t="s">
         <v>41</v>
       </c>
     </row>
